--- a/LISTAS_ORDENADAS/MA/Soportes y escuadras/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Soportes y escuadras/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,14 +875,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45202.60864177897</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="19">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1013,20 +1008,6 @@
       <c r="E21" s="6" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="34.5" customHeight="1" s="19" thickBot="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
@@ -1092,16 +1073,6 @@
         <v>248</v>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
@@ -1111,11 +1082,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
